--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2106,6 +2106,2444 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>118144074</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>493500</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6933356</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>118143882</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>493522</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6933299</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>118143685</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79563</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>493528</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6933269</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>118143946</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>493510</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6933307</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>118143702</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79599</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>493528</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6933269</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>118144019</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>493491</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6933331</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>118143660</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>493572</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6933230</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>118143768</v>
+      </c>
+      <c r="B22" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>493527</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6933285</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>118143890</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>493516</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6933301</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>118143873</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>493516</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6933276</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118144058</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79563</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>493490</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6933361</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118143903</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97859</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>493512</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6933332</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118144096</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78482</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>493487</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6933365</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118143920</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96793</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>493509</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6933305</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118143913</v>
+      </c>
+      <c r="B29" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>493512</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6933338</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118143936</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>493511</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6933306</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118143834</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79591</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>493529</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6933296</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118144110</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>493488</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6933366</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118143673</v>
+      </c>
+      <c r="B33" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>493528</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6933250</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118144130</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57288</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>493487</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6933366</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118143856</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97859</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>493516</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6933274</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118143959</v>
+      </c>
+      <c r="B36" t="n">
+        <v>97838</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>493502</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6933316</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-06-30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -6485,10 +6485,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118212961</v>
+        <v>118220989</v>
       </c>
       <c r="B54" t="n">
-        <v>57290</v>
+        <v>56494</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6501,16 +6501,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6523,7 +6523,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>stationär</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -6533,10 +6533,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>494025</v>
+        <v>493963</v>
       </c>
       <c r="R54" t="n">
-        <v>6932591</v>
+        <v>6932620</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6588,17 +6588,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118212986</v>
+        <v>118221015</v>
       </c>
       <c r="B55" t="n">
-        <v>57290</v>
+        <v>79565</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6611,31 +6611,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6643,10 +6638,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>493839</v>
+        <v>493685</v>
       </c>
       <c r="R55" t="n">
-        <v>6932869</v>
+        <v>6932972</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6681,17 +6676,13 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack på flera träd</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6703,17 +6694,17 @@
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118221015</v>
+        <v>118212961</v>
       </c>
       <c r="B56" t="n">
-        <v>79565</v>
+        <v>57290</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6726,26 +6717,31 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -6753,10 +6749,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>493685</v>
+        <v>494025</v>
       </c>
       <c r="R56" t="n">
-        <v>6932972</v>
+        <v>6932591</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6797,7 +6793,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6809,17 +6804,17 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118220989</v>
+        <v>118212986</v>
       </c>
       <c r="B57" t="n">
-        <v>56494</v>
+        <v>57290</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6832,16 +6827,16 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6854,7 +6849,7 @@
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
@@ -6864,10 +6859,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>493963</v>
+        <v>493839</v>
       </c>
       <c r="R57" t="n">
-        <v>6932620</v>
+        <v>6932869</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6902,6 +6897,11 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack på flera träd</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7368,10 +7368,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118203892</v>
+        <v>118229948</v>
       </c>
       <c r="B62" t="n">
-        <v>95394</v>
+        <v>78484</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7384,41 +7384,40 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Gillån (Gillån), Jmt</t>
+          <t>Gillån, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>493885</v>
+        <v>493707</v>
       </c>
       <c r="R62" t="n">
-        <v>6932797</v>
+        <v>6932902</v>
       </c>
       <c r="S62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7445,19 +7444,9 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>21:17</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>21:17</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7478,17 +7467,17 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson, Marielle Löthman, Anders Wännström</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118229948</v>
+        <v>118203892</v>
       </c>
       <c r="B63" t="n">
-        <v>78484</v>
+        <v>95394</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7501,40 +7490,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Gillån, Jmt</t>
+          <t>Gillån (Gillån), Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>493707</v>
+        <v>493885</v>
       </c>
       <c r="R63" t="n">
-        <v>6932902</v>
+        <v>6932797</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7561,9 +7551,19 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>21:17</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>21:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7584,17 +7584,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Erik Wilhelmsson, Marielle Löthman, Anders Wännström</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118220459</v>
+        <v>118212999</v>
       </c>
       <c r="B64" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7603,39 +7603,35 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7643,10 +7639,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>493884</v>
+        <v>493721</v>
       </c>
       <c r="R64" t="n">
-        <v>6932739</v>
+        <v>6933113</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7687,7 +7683,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7706,7 +7701,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118212999</v>
+        <v>118220900</v>
       </c>
       <c r="B65" t="n">
         <v>57290</v>
@@ -7754,10 +7749,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>493721</v>
+        <v>493678</v>
       </c>
       <c r="R65" t="n">
-        <v>6933113</v>
+        <v>6932966</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7809,14 +7804,14 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118220900</v>
+        <v>118220445</v>
       </c>
       <c r="B66" t="n">
         <v>57290</v>
@@ -7864,10 +7859,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>493678</v>
+        <v>493884</v>
       </c>
       <c r="R66" t="n">
-        <v>6932966</v>
+        <v>6932739</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7919,17 +7914,17 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118220445</v>
+        <v>118220459</v>
       </c>
       <c r="B67" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7938,35 +7933,39 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -8018,6 +8017,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118200584</v>
+        <v>118212968</v>
       </c>
       <c r="B82" t="n">
-        <v>79601</v>
+        <v>57290</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9631,41 +9631,49 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493671</v>
+        <v>493970</v>
       </c>
       <c r="R82" t="n">
-        <v>6932974</v>
+        <v>6932660</v>
       </c>
       <c r="S82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9692,19 +9700,9 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>19:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9719,22 +9717,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson, Anders Wännström , Marielle Löthman</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118221108</v>
+        <v>118212980</v>
       </c>
       <c r="B83" t="n">
-        <v>79593</v>
+        <v>57290</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9743,30 +9741,35 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6461</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9774,10 +9777,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493709</v>
+        <v>493859</v>
       </c>
       <c r="R83" t="n">
-        <v>6932949</v>
+        <v>6932778</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9818,7 +9821,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9830,14 +9832,14 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118212968</v>
+        <v>118212950</v>
       </c>
       <c r="B84" t="n">
         <v>57290</v>
@@ -9885,10 +9887,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>493970</v>
+        <v>494119</v>
       </c>
       <c r="R84" t="n">
-        <v>6932660</v>
+        <v>6932546</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9947,10 +9949,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118212980</v>
+        <v>118220612</v>
       </c>
       <c r="B85" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9959,35 +9961,39 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -9995,10 +10001,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493859</v>
+        <v>493642</v>
       </c>
       <c r="R85" t="n">
-        <v>6932778</v>
+        <v>6933037</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10039,6 +10045,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10057,10 +10064,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118212950</v>
+        <v>118200584</v>
       </c>
       <c r="B86" t="n">
-        <v>57290</v>
+        <v>79601</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10069,49 +10076,41 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>494119</v>
+        <v>493671</v>
       </c>
       <c r="R86" t="n">
-        <v>6932546</v>
+        <v>6932974</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10138,9 +10137,19 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10155,22 +10164,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Erik Wilhelmsson, Anders Wännström , Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118220612</v>
+        <v>118221108</v>
       </c>
       <c r="B87" t="n">
-        <v>97846</v>
+        <v>79593</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10179,39 +10188,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493642</v>
+        <v>493709</v>
       </c>
       <c r="R87" t="n">
-        <v>6933037</v>
+        <v>6932949</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -6926,10 +6926,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118220535</v>
+        <v>118221116</v>
       </c>
       <c r="B58" t="n">
-        <v>97846</v>
+        <v>79593</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6938,39 +6938,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -6978,10 +6969,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>493912</v>
+        <v>493725</v>
       </c>
       <c r="R58" t="n">
-        <v>6932692</v>
+        <v>6932894</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7034,17 +7025,17 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118221116</v>
+        <v>118229922</v>
       </c>
       <c r="B59" t="n">
-        <v>79593</v>
+        <v>74596</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7053,25 +7044,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6461</v>
+        <v>6440</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7080,14 +7071,14 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Gillån, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>493725</v>
+        <v>493781</v>
       </c>
       <c r="R59" t="n">
-        <v>6932894</v>
+        <v>6932968</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7135,22 +7126,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118229922</v>
+        <v>118220949</v>
       </c>
       <c r="B60" t="n">
-        <v>74596</v>
+        <v>57290</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7163,37 +7154,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gillån, Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>493781</v>
+        <v>493693</v>
       </c>
       <c r="R60" t="n">
-        <v>6932968</v>
+        <v>6933146</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7228,35 +7224,39 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Färska ringhack på två tallar</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118220949</v>
+        <v>118220535</v>
       </c>
       <c r="B61" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7265,35 +7265,39 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7301,10 +7305,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>493693</v>
+        <v>493912</v>
       </c>
       <c r="R61" t="n">
-        <v>6933146</v>
+        <v>6932692</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7339,17 +7343,13 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Färska ringhack på två tallar</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -7361,7 +7361,7 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -8261,10 +8261,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>118214720</v>
+        <v>118221121</v>
       </c>
       <c r="B70" t="n">
-        <v>97846</v>
+        <v>96801</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8273,37 +8273,29 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
@@ -8313,10 +8305,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>493870</v>
+        <v>494114</v>
       </c>
       <c r="R70" t="n">
-        <v>6932777</v>
+        <v>6932565</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8369,14 +8361,14 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>118220588</v>
+        <v>118214720</v>
       </c>
       <c r="B71" t="n">
         <v>97846</v>
@@ -8411,7 +8403,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -8428,10 +8420,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>493638</v>
+        <v>493870</v>
       </c>
       <c r="R71" t="n">
-        <v>6933055</v>
+        <v>6932777</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8484,17 +8476,17 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>118221121</v>
+        <v>118220588</v>
       </c>
       <c r="B72" t="n">
-        <v>96801</v>
+        <v>97846</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8503,29 +8495,37 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="N72" t="inlineStr"/>
@@ -8535,10 +8535,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>494114</v>
+        <v>493638</v>
       </c>
       <c r="R72" t="n">
-        <v>6932565</v>
+        <v>6933055</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8591,7 +8591,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -9619,10 +9619,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>118212968</v>
+        <v>118200584</v>
       </c>
       <c r="B82" t="n">
-        <v>57290</v>
+        <v>79601</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9631,49 +9631,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>493970</v>
+        <v>493671</v>
       </c>
       <c r="R82" t="n">
-        <v>6932660</v>
+        <v>6932974</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9700,9 +9692,19 @@
           <t>2024-07-03</t>
         </is>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-07-03</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>19:21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9717,22 +9719,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Erik Wilhelmsson, Anders Wännström , Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>118212980</v>
+        <v>118221108</v>
       </c>
       <c r="B83" t="n">
-        <v>57290</v>
+        <v>79593</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9741,35 +9743,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -9777,10 +9774,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>493859</v>
+        <v>493709</v>
       </c>
       <c r="R83" t="n">
-        <v>6932778</v>
+        <v>6932949</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9821,6 +9818,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -9832,14 +9830,14 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
+          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>118212950</v>
+        <v>118212968</v>
       </c>
       <c r="B84" t="n">
         <v>57290</v>
@@ -9887,10 +9885,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>494119</v>
+        <v>493970</v>
       </c>
       <c r="R84" t="n">
-        <v>6932546</v>
+        <v>6932660</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9949,10 +9947,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>118220612</v>
+        <v>118212980</v>
       </c>
       <c r="B85" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9961,39 +9959,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
@@ -10001,10 +9995,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>493642</v>
+        <v>493859</v>
       </c>
       <c r="R85" t="n">
-        <v>6933037</v>
+        <v>6932778</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10045,7 +10039,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -10064,10 +10057,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>118200584</v>
+        <v>118212950</v>
       </c>
       <c r="B86" t="n">
-        <v>79601</v>
+        <v>57290</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10076,41 +10069,49 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Svarttjärnbäcken (Svarttjärnbäcken), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>493671</v>
+        <v>494119</v>
       </c>
       <c r="R86" t="n">
-        <v>6932974</v>
+        <v>6932546</v>
       </c>
       <c r="S86" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10137,19 +10138,9 @@
           <t>2024-07-03</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>19:21</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-07-03</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>19:21</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10164,22 +10155,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erik Wilhelmsson, Anders Wännström , Marielle Löthman</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>118221108</v>
+        <v>118220612</v>
       </c>
       <c r="B87" t="n">
-        <v>79593</v>
+        <v>97846</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10188,30 +10179,39 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
@@ -10219,10 +10219,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>493709</v>
+        <v>493642</v>
       </c>
       <c r="R87" t="n">
-        <v>6932949</v>
+        <v>6933037</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10275,7 +10275,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman, Anders Wännström , Erik Wilhelmsson</t>
+          <t>Marielle Löthman, Erik Wilhelmsson, Anders Wännström</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118311071</v>
+        <v>118301400</v>
       </c>
       <c r="B93" t="n">
-        <v>78484</v>
+        <v>57290</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10868,37 +10868,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493754</v>
+        <v>494110</v>
       </c>
       <c r="R93" t="n">
-        <v>6932820</v>
+        <v>6932544</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10928,18 +10930,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10958,10 +10969,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118311123</v>
+        <v>118311101</v>
       </c>
       <c r="B94" t="n">
-        <v>78220</v>
+        <v>97846</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10970,30 +10981,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11001,10 +11021,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493786</v>
+        <v>493795</v>
       </c>
       <c r="R94" t="n">
-        <v>6932794</v>
+        <v>6932751</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11064,10 +11084,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118301316</v>
+        <v>118311089</v>
       </c>
       <c r="B95" t="n">
-        <v>57290</v>
+        <v>79593</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11076,43 +11096,41 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493963</v>
+        <v>493752</v>
       </c>
       <c r="R95" t="n">
-        <v>6932603</v>
+        <v>6932827</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11142,27 +11160,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11181,10 +11190,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118301215</v>
+        <v>118311057</v>
       </c>
       <c r="B96" t="n">
-        <v>78220</v>
+        <v>78484</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11197,34 +11206,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493902</v>
+        <v>493731</v>
       </c>
       <c r="R96" t="n">
-        <v>6932572</v>
+        <v>6932864</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11254,27 +11266,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11293,10 +11296,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118300886</v>
+        <v>118311123</v>
       </c>
       <c r="B97" t="n">
-        <v>97846</v>
+        <v>78220</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11305,47 +11308,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>493804</v>
+        <v>493786</v>
       </c>
       <c r="R97" t="n">
-        <v>6932692</v>
+        <v>6932794</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11375,27 +11372,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
+      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11414,10 +11402,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118311101</v>
+        <v>118301215</v>
       </c>
       <c r="B98" t="n">
-        <v>97846</v>
+        <v>78220</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11426,50 +11414,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493795</v>
+        <v>493902</v>
       </c>
       <c r="R98" t="n">
-        <v>6932751</v>
+        <v>6932572</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11499,18 +11475,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11529,10 +11514,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118301400</v>
+        <v>118311071</v>
       </c>
       <c r="B99" t="n">
-        <v>57290</v>
+        <v>78484</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11545,39 +11530,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>494110</v>
+        <v>493754</v>
       </c>
       <c r="R99" t="n">
-        <v>6932544</v>
+        <v>6932820</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11607,27 +11590,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11646,10 +11620,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118311110</v>
+        <v>118301316</v>
       </c>
       <c r="B100" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11658,50 +11632,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493764</v>
+        <v>493963</v>
       </c>
       <c r="R100" t="n">
-        <v>6932815</v>
+        <v>6932603</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11731,18 +11698,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11761,10 +11737,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118301209</v>
+        <v>118300886</v>
       </c>
       <c r="B101" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11773,38 +11749,47 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493902</v>
+        <v>493804</v>
       </c>
       <c r="R101" t="n">
-        <v>6932572</v>
+        <v>6932692</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11873,10 +11858,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118311057</v>
+        <v>118311110</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11885,30 +11870,39 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
@@ -11916,10 +11910,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493731</v>
+        <v>493764</v>
       </c>
       <c r="R102" t="n">
-        <v>6932864</v>
+        <v>6932815</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11979,10 +11973,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118311089</v>
+        <v>118301209</v>
       </c>
       <c r="B103" t="n">
-        <v>79593</v>
+        <v>78221</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11991,41 +11985,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6461</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493752</v>
+        <v>493902</v>
       </c>
       <c r="R103" t="n">
-        <v>6932827</v>
+        <v>6932572</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12055,18 +12046,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -11737,10 +11737,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118300886</v>
+        <v>118301209</v>
       </c>
       <c r="B101" t="n">
-        <v>97846</v>
+        <v>78221</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11749,47 +11749,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493804</v>
+        <v>493902</v>
       </c>
       <c r="R101" t="n">
-        <v>6932692</v>
+        <v>6932572</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11858,7 +11849,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118311110</v>
+        <v>118300886</v>
       </c>
       <c r="B102" t="n">
         <v>97846</v>
@@ -11893,7 +11884,7 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -11901,19 +11892,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493764</v>
+        <v>493804</v>
       </c>
       <c r="R102" t="n">
-        <v>6932815</v>
+        <v>6932692</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11943,18 +11931,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11973,10 +11970,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118301209</v>
+        <v>118311110</v>
       </c>
       <c r="B103" t="n">
-        <v>78221</v>
+        <v>97846</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11985,38 +11982,50 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493902</v>
+        <v>493764</v>
       </c>
       <c r="R103" t="n">
-        <v>6932572</v>
+        <v>6932815</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12046,27 +12055,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118301400</v>
+        <v>118300886</v>
       </c>
       <c r="B93" t="n">
-        <v>57290</v>
+        <v>97846</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10864,31 +10864,35 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10897,10 +10901,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>494110</v>
+        <v>493804</v>
       </c>
       <c r="R93" t="n">
-        <v>6932544</v>
+        <v>6932692</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10969,10 +10973,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118311101</v>
+        <v>118311057</v>
       </c>
       <c r="B94" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10981,39 +10985,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11021,10 +11016,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493795</v>
+        <v>493731</v>
       </c>
       <c r="R94" t="n">
-        <v>6932751</v>
+        <v>6932864</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11190,10 +11185,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118311057</v>
+        <v>118311101</v>
       </c>
       <c r="B96" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11202,30 +11197,39 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
@@ -11233,10 +11237,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493731</v>
+        <v>493795</v>
       </c>
       <c r="R96" t="n">
-        <v>6932864</v>
+        <v>6932751</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11296,10 +11300,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118311123</v>
+        <v>118301209</v>
       </c>
       <c r="B97" t="n">
-        <v>78220</v>
+        <v>78221</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11312,37 +11316,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>493786</v>
+        <v>493902</v>
       </c>
       <c r="R97" t="n">
-        <v>6932794</v>
+        <v>6932572</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11372,18 +11373,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
       <c r="AE97" t="b">
         <v>0</v>
       </c>
-      <c r="AF97" t="inlineStr"/>
       <c r="AG97" t="b">
         <v>0</v>
       </c>
@@ -11402,7 +11412,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118301215</v>
+        <v>118311123</v>
       </c>
       <c r="B98" t="n">
         <v>78220</v>
@@ -11436,16 +11446,19 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493902</v>
+        <v>493786</v>
       </c>
       <c r="R98" t="n">
-        <v>6932572</v>
+        <v>6932794</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11475,27 +11488,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
       </c>
@@ -11514,10 +11518,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118311071</v>
+        <v>118311110</v>
       </c>
       <c r="B99" t="n">
-        <v>78484</v>
+        <v>97846</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11526,30 +11530,39 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
@@ -11557,10 +11570,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493754</v>
+        <v>493764</v>
       </c>
       <c r="R99" t="n">
-        <v>6932820</v>
+        <v>6932815</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11620,10 +11633,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118301316</v>
+        <v>118301215</v>
       </c>
       <c r="B100" t="n">
-        <v>57290</v>
+        <v>78220</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11636,39 +11649,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493963</v>
+        <v>493902</v>
       </c>
       <c r="R100" t="n">
-        <v>6932603</v>
+        <v>6932572</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11737,10 +11745,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118301209</v>
+        <v>118301400</v>
       </c>
       <c r="B101" t="n">
-        <v>78221</v>
+        <v>57290</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11753,34 +11761,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>493902</v>
+        <v>494110</v>
       </c>
       <c r="R101" t="n">
-        <v>6932572</v>
+        <v>6932544</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11849,10 +11862,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118300886</v>
+        <v>118311071</v>
       </c>
       <c r="B102" t="n">
-        <v>97846</v>
+        <v>78484</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11861,47 +11874,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493804</v>
+        <v>493754</v>
       </c>
       <c r="R102" t="n">
-        <v>6932692</v>
+        <v>6932820</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11931,27 +11938,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD102" t="b">
         <v>0</v>
       </c>
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
@@ -11970,10 +11968,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118311110</v>
+        <v>118301316</v>
       </c>
       <c r="B103" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11982,50 +11980,43 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493764</v>
+        <v>493963</v>
       </c>
       <c r="R103" t="n">
-        <v>6932815</v>
+        <v>6932603</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12055,18 +12046,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -10852,10 +10852,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>118300886</v>
+        <v>118301316</v>
       </c>
       <c r="B93" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10864,35 +10864,31 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10901,10 +10897,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>493804</v>
+        <v>493963</v>
       </c>
       <c r="R93" t="n">
-        <v>6932692</v>
+        <v>6932603</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10973,10 +10969,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>118311057</v>
+        <v>118311101</v>
       </c>
       <c r="B94" t="n">
-        <v>78484</v>
+        <v>97853</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10985,30 +10981,39 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
@@ -11016,10 +11021,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>493731</v>
+        <v>493795</v>
       </c>
       <c r="R94" t="n">
-        <v>6932864</v>
+        <v>6932751</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11079,10 +11084,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>118311089</v>
+        <v>118300886</v>
       </c>
       <c r="B95" t="n">
-        <v>79593</v>
+        <v>97853</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11091,41 +11096,47 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>493752</v>
+        <v>493804</v>
       </c>
       <c r="R95" t="n">
-        <v>6932827</v>
+        <v>6932692</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11155,18 +11166,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD95" t="b">
         <v>0</v>
       </c>
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
       </c>
@@ -11185,10 +11205,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>118311101</v>
+        <v>118301209</v>
       </c>
       <c r="B96" t="n">
-        <v>97846</v>
+        <v>78228</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11197,50 +11217,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>493795</v>
+        <v>493902</v>
       </c>
       <c r="R96" t="n">
-        <v>6932751</v>
+        <v>6932572</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11270,18 +11278,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
@@ -11300,10 +11317,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>118301209</v>
+        <v>118301215</v>
       </c>
       <c r="B97" t="n">
-        <v>78221</v>
+        <v>78227</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11316,21 +11333,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11412,10 +11429,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>118311123</v>
+        <v>118311110</v>
       </c>
       <c r="B98" t="n">
-        <v>78220</v>
+        <v>97853</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11424,30 +11441,39 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
@@ -11455,10 +11481,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>493786</v>
+        <v>493764</v>
       </c>
       <c r="R98" t="n">
-        <v>6932794</v>
+        <v>6932815</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11518,10 +11544,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>118311110</v>
+        <v>118301400</v>
       </c>
       <c r="B99" t="n">
-        <v>97846</v>
+        <v>57290</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11530,50 +11556,43 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Struldalen, Jmt</t>
+          <t>Struldalen (Struldalen), Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>493764</v>
+        <v>494110</v>
       </c>
       <c r="R99" t="n">
-        <v>6932815</v>
+        <v>6932544</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11603,18 +11622,27 @@
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
@@ -11633,10 +11661,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>118301215</v>
+        <v>118311071</v>
       </c>
       <c r="B100" t="n">
-        <v>78220</v>
+        <v>78491</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11649,34 +11677,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>493902</v>
+        <v>493754</v>
       </c>
       <c r="R100" t="n">
-        <v>6932572</v>
+        <v>6932820</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11706,27 +11737,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
@@ -11745,10 +11767,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>118301400</v>
+        <v>118311089</v>
       </c>
       <c r="B101" t="n">
-        <v>57290</v>
+        <v>79600</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11757,43 +11779,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6461</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>494110</v>
+        <v>493752</v>
       </c>
       <c r="R101" t="n">
-        <v>6932544</v>
+        <v>6932827</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11823,27 +11843,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
@@ -11862,10 +11873,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>118311071</v>
+        <v>118311123</v>
       </c>
       <c r="B102" t="n">
-        <v>78484</v>
+        <v>78227</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11878,21 +11889,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11905,10 +11916,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>493754</v>
+        <v>493786</v>
       </c>
       <c r="R102" t="n">
-        <v>6932820</v>
+        <v>6932794</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11968,10 +11979,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>118301316</v>
+        <v>118311057</v>
       </c>
       <c r="B103" t="n">
-        <v>57290</v>
+        <v>78491</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11984,39 +11995,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>493963</v>
+        <v>493731</v>
       </c>
       <c r="R103" t="n">
-        <v>6932603</v>
+        <v>6932864</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12046,27 +12055,18 @@
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-07-08</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -3328,7 +3328,7 @@
         <v>118144130</v>
       </c>
       <c r="B26" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>118212936</v>
       </c>
       <c r="B52" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>118212961</v>
       </c>
       <c r="B56" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>118212986</v>
       </c>
       <c r="B57" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>118220949</v>
       </c>
       <c r="B60" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>118212999</v>
       </c>
       <c r="B64" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>118220900</v>
       </c>
       <c r="B65" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>118220445</v>
       </c>
       <c r="B66" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>118213057</v>
       </c>
       <c r="B68" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>118213027</v>
       </c>
       <c r="B69" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>118213018</v>
       </c>
       <c r="B75" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>118229936</v>
       </c>
       <c r="B80" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>118212968</v>
       </c>
       <c r="B84" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>118212980</v>
       </c>
       <c r="B85" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>118212950</v>
       </c>
       <c r="B86" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>118213007</v>
       </c>
       <c r="B92" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>118301316</v>
       </c>
       <c r="B93" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10893,7 +10893,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -11547,7 +11547,7 @@
         <v>118301400</v>
       </c>
       <c r="B99" t="n">
-        <v>57290</v>
+        <v>57478</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Struldalen (Struldalen), Jmt</t>
+          <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -6267,7 +6267,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6818,7 +6818,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7818,7 +7818,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -8835,7 +8835,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -10064,7 +10064,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -10749,7 +10749,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -10859,7 +10859,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -11551,7 +11551,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -3328,7 +3328,7 @@
         <v>118144130</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>118212936</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>118212961</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>118212986</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>118220949</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>118212999</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>118220900</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>118220445</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>118213057</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>118213027</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>118213018</v>
       </c>
       <c r="B75" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>118229936</v>
       </c>
       <c r="B80" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>118212968</v>
       </c>
       <c r="B84" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>118212980</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>118212950</v>
       </c>
       <c r="B86" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>118213007</v>
       </c>
       <c r="B92" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>118301316</v>
       </c>
       <c r="B93" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>118301400</v>
       </c>
       <c r="B99" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -3328,7 +3328,7 @@
         <v>118144130</v>
       </c>
       <c r="B26" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>118212936</v>
       </c>
       <c r="B52" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6704,7 +6704,7 @@
         <v>118212961</v>
       </c>
       <c r="B56" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>118212986</v>
       </c>
       <c r="B57" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>118220949</v>
       </c>
       <c r="B60" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>118212999</v>
       </c>
       <c r="B64" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>118220900</v>
       </c>
       <c r="B65" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         <v>118220445</v>
       </c>
       <c r="B66" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>118213057</v>
       </c>
       <c r="B68" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>118213027</v>
       </c>
       <c r="B69" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8831,7 +8831,7 @@
         <v>118213018</v>
       </c>
       <c r="B75" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9392,7 +9392,7 @@
         <v>118229936</v>
       </c>
       <c r="B80" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9840,7 +9840,7 @@
         <v>118212968</v>
       </c>
       <c r="B84" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9950,7 +9950,7 @@
         <v>118212980</v>
       </c>
       <c r="B85" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>118212950</v>
       </c>
       <c r="B86" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10745,7 +10745,7 @@
         <v>118213007</v>
       </c>
       <c r="B92" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10855,7 +10855,7 @@
         <v>118301316</v>
       </c>
       <c r="B93" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11547,7 +11547,7 @@
         <v>118301400</v>
       </c>
       <c r="B99" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY103"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12083,6 +12083,463 @@
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>125201834</v>
+      </c>
+      <c r="B104" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Struldalen, Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>493777</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6932758</v>
+      </c>
+      <c r="S104" t="n">
+        <v>5</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>125202291</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Struldalen, Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>493906</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6932770</v>
+      </c>
+      <c r="S105" t="n">
+        <v>5</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>125202550</v>
+      </c>
+      <c r="B106" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Struldalen, Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>493928</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6932739</v>
+      </c>
+      <c r="S106" t="n">
+        <v>5</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>125202968</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79920</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Struldalen, Struldalen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>493871</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6932685</v>
+      </c>
+      <c r="S107" t="n">
+        <v>5</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-05-18</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>18:12</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12085,10 +12085,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125201834</v>
+        <v>125202291</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12097,47 +12097,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493777</v>
+        <v>493906</v>
       </c>
       <c r="R104" t="n">
-        <v>6932758</v>
+        <v>6932770</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12206,7 +12197,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125202291</v>
+        <v>125202550</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -12246,10 +12237,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493906</v>
+        <v>493928</v>
       </c>
       <c r="R105" t="n">
-        <v>6932770</v>
+        <v>6932739</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12318,10 +12309,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125202550</v>
+        <v>125201834</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12330,38 +12321,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493928</v>
+        <v>493777</v>
       </c>
       <c r="R106" t="n">
-        <v>6932739</v>
+        <v>6932758</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12085,10 +12085,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125202291</v>
+        <v>125201834</v>
       </c>
       <c r="B104" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12097,38 +12097,47 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493906</v>
+        <v>493777</v>
       </c>
       <c r="R104" t="n">
-        <v>6932770</v>
+        <v>6932758</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12197,7 +12206,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125202550</v>
+        <v>125202291</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -12237,10 +12246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493928</v>
+        <v>493906</v>
       </c>
       <c r="R105" t="n">
-        <v>6932739</v>
+        <v>6932770</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12309,10 +12318,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125201834</v>
+        <v>125202550</v>
       </c>
       <c r="B106" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12321,47 +12330,38 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493777</v>
+        <v>493928</v>
       </c>
       <c r="R106" t="n">
-        <v>6932758</v>
+        <v>6932739</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12206,7 +12206,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125202291</v>
+        <v>125202550</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -12246,10 +12246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493906</v>
+        <v>493928</v>
       </c>
       <c r="R105" t="n">
-        <v>6932770</v>
+        <v>6932739</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12318,10 +12318,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125202550</v>
+        <v>125202968</v>
       </c>
       <c r="B106" t="n">
-        <v>78810</v>
+        <v>79920</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12330,25 +12330,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12358,10 +12358,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493928</v>
+        <v>493871</v>
       </c>
       <c r="R106" t="n">
-        <v>6932739</v>
+        <v>6932685</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12430,10 +12430,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125202968</v>
+        <v>125202291</v>
       </c>
       <c r="B107" t="n">
-        <v>79920</v>
+        <v>78810</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12442,25 +12442,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493871</v>
+        <v>493906</v>
       </c>
       <c r="R107" t="n">
-        <v>6932685</v>
+        <v>6932770</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12206,7 +12206,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125202550</v>
+        <v>125202291</v>
       </c>
       <c r="B105" t="n">
         <v>78810</v>
@@ -12246,10 +12246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493928</v>
+        <v>493906</v>
       </c>
       <c r="R105" t="n">
-        <v>6932739</v>
+        <v>6932770</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12430,7 +12430,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125202291</v>
+        <v>125202550</v>
       </c>
       <c r="B107" t="n">
         <v>78810</v>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493906</v>
+        <v>493928</v>
       </c>
       <c r="R107" t="n">
-        <v>6932770</v>
+        <v>6932739</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12088,7 +12088,7 @@
         <v>125201834</v>
       </c>
       <c r="B104" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12206,10 +12206,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125202291</v>
+        <v>125202968</v>
       </c>
       <c r="B105" t="n">
-        <v>78810</v>
+        <v>80057</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12218,25 +12218,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12246,10 +12246,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493906</v>
+        <v>493871</v>
       </c>
       <c r="R105" t="n">
-        <v>6932770</v>
+        <v>6932685</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12318,10 +12318,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125202968</v>
+        <v>125202550</v>
       </c>
       <c r="B106" t="n">
-        <v>79920</v>
+        <v>78947</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12330,25 +12330,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12358,10 +12358,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493871</v>
+        <v>493928</v>
       </c>
       <c r="R106" t="n">
-        <v>6932685</v>
+        <v>6932739</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12430,10 +12430,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125202550</v>
+        <v>125202291</v>
       </c>
       <c r="B107" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12470,10 +12470,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493928</v>
+        <v>493906</v>
       </c>
       <c r="R107" t="n">
-        <v>6932739</v>
+        <v>6932770</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12085,10 +12085,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125201834</v>
+        <v>125202550</v>
       </c>
       <c r="B104" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12097,47 +12097,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493777</v>
+        <v>493928</v>
       </c>
       <c r="R104" t="n">
-        <v>6932758</v>
+        <v>6932739</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12318,10 +12309,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125202550</v>
+        <v>125201834</v>
       </c>
       <c r="B106" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12330,38 +12321,47 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493928</v>
+        <v>493777</v>
       </c>
       <c r="R106" t="n">
-        <v>6932739</v>
+        <v>6932758</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12085,37 +12085,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125202550</v>
+        <v>125202968</v>
       </c>
       <c r="B104" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80099</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12125,10 +12120,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>493928</v>
+        <v>493871</v>
       </c>
       <c r="R104" t="n">
-        <v>6932739</v>
+        <v>6932685</v>
       </c>
       <c r="S104" t="n">
         <v>5</v>
@@ -12197,37 +12192,32 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125202968</v>
+        <v>125202291</v>
       </c>
       <c r="B105" t="n">
-        <v>80057</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12237,10 +12227,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>493871</v>
+        <v>493906</v>
       </c>
       <c r="R105" t="n">
-        <v>6932685</v>
+        <v>6932770</v>
       </c>
       <c r="S105" t="n">
         <v>5</v>
@@ -12309,59 +12299,45 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125201834</v>
+        <v>125202550</v>
       </c>
       <c r="B106" t="n">
-        <v>98269</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>493777</v>
+        <v>493928</v>
       </c>
       <c r="R106" t="n">
-        <v>6932758</v>
+        <v>6932739</v>
       </c>
       <c r="S106" t="n">
         <v>5</v>
@@ -12430,50 +12406,54 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125202291</v>
+        <v>125201834</v>
       </c>
       <c r="B107" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98324</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Struldalen, Struldalen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>493906</v>
+        <v>493777</v>
       </c>
       <c r="R107" t="n">
-        <v>6932770</v>
+        <v>6932758</v>
       </c>
       <c r="S107" t="n">
         <v>5</v>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -12409,7 +12409,7 @@
         <v>125201834</v>
       </c>
       <c r="B107" t="n">
-        <v>98324</v>
+        <v>98331</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 26959-2024 artfynd.xlsx
+++ b/artfynd/A 26959-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY118"/>
+  <dimension ref="A1:AZ118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113165</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113180</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113193</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143768</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143873</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118144096</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1486,6 +1526,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118200788</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1593,6 +1638,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118201335</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1700,6 +1750,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118201624</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1807,6 +1862,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118206494</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1908,6 +1968,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118229948</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2009,6 +2074,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311057</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2110,6 +2180,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311071</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,6 +2292,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118201857</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2324,6 +2404,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118202412</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2425,6 +2510,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118229922</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2526,6 +2616,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311123</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2627,6 +2722,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143685</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2732,6 +2832,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118144058</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2839,6 +2944,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118200571</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2940,6 +3050,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118221002</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3041,6 +3156,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118221015</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3142,6 +3262,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113218</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3243,6 +3368,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143834</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3350,6 +3480,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118199619</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3451,6 +3586,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118221108</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3552,6 +3692,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118221116</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3653,6 +3798,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311089</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3754,6 +3904,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143702</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3861,6 +4016,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118200584</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3962,6 +4122,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113057</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4072,6 +4237,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143988</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4182,6 +4352,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118144130</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4287,6 +4462,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212999</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4392,6 +4572,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118213007</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4497,6 +4682,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118213018</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4602,6 +4792,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118213027</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4712,6 +4907,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118213057</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4817,6 +5017,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220900</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4927,6 +5132,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220949</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5037,6 +5247,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118229936</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5142,6 +5357,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220967</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5252,6 +5472,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113138</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5362,6 +5587,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113232</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5472,6 +5702,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113241</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5582,6 +5817,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113250</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5692,6 +5932,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113282</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5802,6 +6047,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113298</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5912,6 +6162,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143673</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6022,6 +6277,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143882</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6132,6 +6392,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143890</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6242,6 +6507,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143913</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6352,6 +6622,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143936</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6462,6 +6737,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143946</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6572,6 +6852,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143959</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6682,6 +6967,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118144019</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6792,6 +7082,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118144074</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6902,6 +7197,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118144110</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7018,6 +7318,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118206596</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7128,6 +7433,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220553</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7238,6 +7548,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220572</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7348,6 +7663,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220588</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7458,6 +7778,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220598</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7568,6 +7893,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220612</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7678,6 +8008,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220626</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7788,6 +8123,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220642</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7898,6 +8238,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220656</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8008,6 +8353,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220676</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8118,6 +8468,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118221033</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8228,6 +8583,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118229929</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8344,6 +8704,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118300867</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8460,6 +8825,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118300886</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8570,6 +8940,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311101</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8680,6 +9055,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118311110</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8796,6 +9176,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125201834</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8912,6 +9297,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125202015</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9014,6 +9404,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113108</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9116,6 +9511,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143920</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9218,6 +9618,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143856</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9320,6 +9725,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118143903</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9427,6 +9837,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118300859</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9528,6 +9943,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118113071</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9640,6 +10060,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118203892</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9747,6 +10172,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118205181</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9854,6 +10284,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118300991</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9961,6 +10396,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118204788</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10068,6 +10508,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125202291</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10175,6 +10620,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125202550</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10282,6 +10732,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118301215</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10389,6 +10844,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118206357</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10496,6 +10956,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118301000</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10603,6 +11068,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125202968</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10720,6 +11190,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118205373</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10825,6 +11300,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212936</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10930,6 +11410,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212950</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11035,6 +11520,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212961</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11140,6 +11630,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212968</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11245,6 +11740,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212980</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11355,6 +11855,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118212986</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11465,6 +11970,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118213112</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11570,6 +12080,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220445</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11682,6 +12197,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118301316</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11794,6 +12314,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118301400</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11899,6 +12424,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220989</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12015,6 +12545,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118204001</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12131,6 +12666,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118204697</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12247,6 +12787,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118206237</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12357,6 +12902,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118214720</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12467,6 +13017,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220459</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12577,6 +13132,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220481</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12687,6 +13247,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220503</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12797,6 +13362,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118220535</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12913,6 +13483,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118301193</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13029,6 +13604,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125202091</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13131,6 +13711,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118221121</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13238,8 +13823,132 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118301209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>